--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_01_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_15_Full_122_Cau/Day_15_Ngan_Hang_Phan_01_21_Cau.xlsx
@@ -672,10 +672,24 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Artifact existence không tự phân chia contribution.
-Phân tích theo nguyên lý thiết kế: Artifact existence không tự phân chia contribution.</t>
+- 1.0đ: Lựa chọn đầy đủ gói bằng chứng gồm PR mã nguồn và báo cáo đo lường CI eval report.
+- 1.0đ: Viết mã định vị (Locators) rõ ràng, có thể kiểm chứng độc lập (PR number/SHA, CI artifact path).
+- 1.0đ: Phân tích đúng giới hạn phân bổ: PR có 2 tác giả nên không được nhận vơ toàn bộ công lao cá nhân.
+- 1.0đ: Viết lại tuyên bố đóng góp chính xác, liêm chính phản ánh đúng vai trò đồng tác giả.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Gói Bằng chứng (Evidence Package) và Mã Định vị (Locators):
+- **Bằng chứng Thay đổi Mã nguồn (Code Change Artifact)**: Git Pull Request bổ sung tầng kiểm tra trích dẫn (citation check).
+  + *Locator*: `git:vlearn-org/ai-agent#pr/142` (Commit SHA: `c3a8f91`, file diff: `src/guardrails/citation_verifier.py`).
+- **Bằng chứng Đo lường Khách quan (Objective Measurement Artifact)**: Báo cáo đánh giá tự động (CI Evaluation Report) trước và sau khi merge PR.
+  + *Locator*: `ci:artifacts/eval-run-982.json#metric=unsupported_claims_rate` (ghi nhận tỷ lệ giảm từ 12% xuống 5% trên cùng tập benchmark cố định 500 ca).
+2. Giới hạn Phân bổ Đóng góp (Attribution Boundary &amp; Intellectual Honesty):
+- **Ranh giới Sở hữu Tập thể (Co-authorship Constraint)**: Đề bài nêu rõ PR do hai người cùng là tác giả (co-authored). Do đó, phát biểu cá nhân 'Tôi đã giảm hallucination' là **quá phạm vi bằng chứng (over-attribution)** và thiếu tính liêm chính học thuật.
+- **Tuyên bố Chuẩn mực Hợp lệ**: Bắt buộc phải tuyên bố dưới dạng đóng góp chung hoặc ghi rõ phần việc cụ thể của mình:
+  'Tôi đồng tác giả PR #142 (phụ trách viết thuật toán regex/NLI trích xuất citation),   góp phần cùng đồng nghiệp giảm tỷ lệ khẳng định không căn cứ (unsupported rate) từ 12% xuống 5% theo báo cáo CI #982.'
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản trị Bằng chứng trong Hậu kiểm (Evidence-based Retrospective &amp; Attribution Limits): Một khẳng định thành tích kỹ thuật chỉ có giá trị khi có bằng chứng vật lý kèm mã định vị (URL, Commit SHA, Report ID). Đặc biệt, sự tồn tại của artifact (PR) không tự động chứng minh toàn bộ công lao thuộc về một cá nhân. Khi có đồng tác giả, việc minh bạch ranh giới đóng góp là chuẩn mực đạo đức kỹ nghệ và ngăn chặn tranh chấp nội bộ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Postmortem Guidelines: Evidence-based Claims &amp; IEEE Code of Ethics: Accurate Attribution</t>
         </is>
       </c>
     </row>
@@ -802,10 +816,27 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Note phải đủ cụ thể để người khác kiểm lại.
-Phân tích theo nguyên lý thiết kế: Note phải đủ cụ thể để người khác kiểm lại.</t>
+- 1.0đ: Trình bày sự kiện kỹ thuật khách quan, không thêm thắt cảm xúc tiêu cực.
+- 1.0đ: Trích dẫn bằng chứng cụ thể từ log (Validator không chạy ở entrypoint dẫn đến thiếu customer_id).
+- 1.0đ: Thiết lập thực hành GIỮ (bảo vệ downstream validation) và TRÁNH (không bỏ sót middleware ở route).
+- 1.0đ: Giữ vững ranh giới bằng chứng: kiên quyết không suy diễn quá đà về toàn bộ hệ thống hay cá nhân.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Viết Note Sự kiện – Ví dụ – Giữ/Tránh (Event - Example - Keep/Avoid Note) Chuẩn mực, Không Suy đoán Quá Bằng chứng:
+1. **Sự kiện Kỹ thuật (Observable Technical Event)**:
+- Buổi demo tính năng bị thất bại (crash với mã lỗi HTTP 500) khi người dùng gửi một yêu cầu hợp lệ do request payload bị thiếu trường bắt buộc `customer_id`.
+2. **Ví dụ Bằng chứng (Concrete Telemetry Evidence)**:
+- Dòng log server tại thời điểm demo (`trace_id: demo-err-881` lúc 14:22):   `[ERROR] EntrypointHandler dispatched request without passing through CustomerValidator middleware. Downstream UserService thrown MissingArgumentException: customer_id is null.`
+  Bằng chứng xác nhận rõ: Bộ kiểm thực dữ liệu (Validator) đã hoàn toàn bị bỏ qua tại cổng tiếp nhận entrypoint của route demo này.
+3. **Thực hành Cần Giữ (Keep Practice)**:
+- **GIỮ**: Tiếp tục duy trì các quy tắc nghiệp vụ nghiêm ngặt kiểm tra tính bắt buộc của `customer_id` ở các downstream services.
+4. **Thực hành Cần Tránh (Avoid Practice)**:
+- **TRÁNH**: Tránh việc cấu hình route mới mà không gắn Global Validation Middleware tại API Gateway. Tránh giả định ngây thơ rằng client sẽ luôn gửi đủ các trường dữ liệu mà không có lớp schema validation cưỡng chế ở cửa ngõ.
+5. **Ranh giới Bằng chứng (Non-overclaiming Boundary)**:
+- Tuyệt đối không suy diễn cảm tính: 'Toàn bộ kiến trúc bảo mật bị hỏng' hoặc 'Lập trình viên cố tình gian lận'. Bằng chứng chỉ chứng minh duy nhất: Một route handler cụ thể bị thiếu middleware validator.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Ghi chép Sự thật Khách quan trong Retrospective (Fact vs Speculation in SRE Notes): Khi sự cố xảy ra trong một buổi demo quan trọng, cảm xúc thất vọng dễ dẫn đến những kết luận thổi phồng hoặc đổ lỗi hoang mang. Cấu trúc 'Sự kiện - Ví dụ - Giữ - Tránh' neo chặt suy nghĩ của kỹ sư vào sự thật có log chứng minh (Validator không chạy ở entrypoint), từ đó đưa ra giải pháp hạ tầng đúng đắn (Global Middleware) thay vì suy đoán mơ hồ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Etsy Debriefing Facilitation Guide &amp; Google SRE Book: Postmortem Culture</t>
         </is>
       </c>
     </row>
@@ -836,10 +867,24 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ cấu trúc: khi bối cảnh nào, evidence gì, lần sau làm gì.
-Phân tích theo nguyên lý thiết kế: Giữ cấu trúc: khi bối cảnh nào, evidence gì, lần sau làm gì.</t>
+- 1.0đ: Xác định đúng bối cảnh kỹ thuật áp dụng (hệ thống RAG phụ thuộc corpus động).
+- 1.0đ: Trình bày bằng chứng thực nghiệm rõ ràng từ sự cố chatbot (test pass trên corpus cũ, fail trên prod mới).
+- 1.0đ: Đúc kết quy tắc hành động tái sử dụng mạch lạc (Corpus-Prompt Parity Rule / Version freezing).
+- 1.0đ: Chỉ rõ ranh giới giới hạn không áp dụng (các tác vụ kiến thức tĩnh, văn bản tự chứa).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Rút Bài học Tái sử dụng (Transferable Lesson) có Bối cảnh và Ranh giới Giới hạn:
+1. **Bối cảnh Kỹ thuật (Applicable Context)**:
+- Áp dụng cho các hệ thống AI ứng dụng mô hình RAG (Retrieval-Augmented Generation) hoặc Agent phụ thuộc vào cơ sở tri thức bên ngoài liên tục biến động (Dynamic Knowledge Base).
+2. **Bằng chứng Thực tế Đúc kết (Empirical Evidence)**:
+- Trong dự án chatbot nội bộ, toàn bộ các bài test prompt đều đạt 100% trong môi trường CI/staging, nhưng khi phát hành ra production thì thất bại hàng loạt do kho ngữ liệu (retrieval corpus) trên production đã được cập nhật văn bản mới trong khi môi trường test vẫn chạy trên snapshot corpus cũ của tháng trước.
+3. **Bài học Hành động Tái sử dụng (Actionable Transferable Rule)**:
+- **Nguyên tắc Đồng bộ Phiên bản Ngữ liệu (Corpus-Prompt Parity Rule)**: Mỗi khi chạy kiểm thử đánh giá prompt, bắt buộc phải đồng bộ và gắn thẻ phiên bản bất biến (immutable hash tag) của cả Prompt VÀ Ngữ liệu tham chiếu: `eval_run = {prompt_hash, corpus_snapshot_id}`. Tuyệt đối cấm đánh giá prompt trên một corpus tĩnh độc lập với trạng thái dữ liệu production.
+4. **Ranh giới và Giới hạn Áp dụng (Boundary of Applicability)**:
+- Bài học này **KHÔNG ÁP DỤNG** cho các tác vụ suy luận logic đóng kín hoặc kiến thức tĩnh phổ quát (như giải toán toán học GSM8K, tóm tắt đoạn văn bản tự chứa do người dùng trực tiếp đưa vào), nơi kết quả không phụ thuộc vào tầng truy xuất cơ sở dữ liệu động.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đúc kết Bài học Chuyển giao trong Công nghệ Phần mềm (Transferable Learning with Scoped Boundaries): Một bài học sau sự cố chỉ có giá trị khi nó có thể tái sử dụng cho các dự án khác. Cấu trúc chuẩn của một bài học phải gồm 4 phần: Bối cảnh áp dụng, Bằng chứng sự cố, Quy tắc hành động cụ thể, và quan trọng nhất là Ranh giới giới hạn - chỉ rõ khi nào quy tắc này không nên áp dụng để tránh giáo điều máy móc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Fowler: Continuous Integration &amp; Google SRE Workbook: Learning from Incidents</t>
         </is>
       </c>
     </row>
@@ -870,10 +915,25 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bài học cần có bối cảnh và hành động tái sử dụng.
-Phân tích theo nguyên lý thiết kế: Bài học cần có bối cảnh và hành động tái sử dụng.</t>
+- 1.0đ: Phân tích đúng sai lầm cốt tử: merge prompt khi unpinned eval set làm mất khả năng quy kết nguyên nhân tăng điểm.
+- 1.0đ: Thiết lập quy tắc đóng băng bộ dữ liệu đánh giá (Frozen Eval Benchmark với mã hash cố định).
+- 1.0đ: Đưa ra nguyên tắc kiểm soát đơn biến bắt buộc cho các đợt thử nghiệm tiếp theo.
+- 1.0đ: Xác định rõ ranh giới áp dụng giữa cổng phát hành chính thức (nghiêm ngặt) và giai đoạn khám phá.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Rút Bài học Áp dụng cho Lần Thay đổi Tiếp theo (Actionable Lesson for Prompt Evolution):
+1. **Bối cảnh &amp; Điểm mù Nghiệp vụ (The Confounded Evaluation Flaw)**:
+- Nhóm đã thực hiện merge prompt mới vào hệ thống mà không khóa cố định phiên bản tập dữ liệu đánh giá (unpinned eval set). Mặc dù điểm số tổng thể tăng, nhưng nhóm rơi vào tình trạng mù mờ thông tin: không thể chứng minh được mức tăng điểm đó là do Prompt mới thực sự thông minh hơn, hay do tập dữ liệu đánh giá vô tình bị thay đổi (ví dụ: bị thêm các ca dễ hơn hoặc bớt các ca khó).
+2. **Bài học Hành động Chuẩn mực cho Lần Thay đổi Kế tiếp (Actionable Protocol)**:
+- **Nguyên tắc Đóng băng Bộ Đánh giá (Frozen Evaluation Benchmark Invariant)**: Trước khi tiến hành bất kỳ thử nghiệm thay đổi prompt nào, tập dữ liệu đánh giá bắt buộc phải được đóng băng bất biến dưới dạng một Golden Release Set có gán mã hash (ví dụ: `golden_eval_v2.1_sha256`).
+- **Quy tắc Kiểm soát Đơn Biến (Single-variable Experimentation Rule)**: Trong một đợt thử nghiệm, **CHỈ ĐƯỢC PHÉP THAY ĐỔI MỘT BIẾN SỐ DUY NHẤT**:
+  + Nếu muốn đo lường Prompt: Giữ nguyên vẹn 100% Eval Set và Model Version, chỉ đổi Prompt text.
+  + Nếu muốn mở rộng Eval Set: Giữ nguyên Prompt cũ, chạy trên cả hai tập eval để đo lường độ lệch đường cơ sở (re-baselining).
+3. **Ranh giới Áp dụng (Boundary)**:
+- Quy tắc này áp dụng tuyệt đối cho các đợt phát hành mã nguồn chính thức (Release Gate). Đối với giai đoạn nghiên cứu khám phá ban đầu (Exploratory Prompting), kỹ sư có thể thử nghiệm linh hoạt nhưng không được dùng kết quả đó để làm căn cứ nghiệm thu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Kiểm soát Đơn biến trong Khoa học Đánh giá AI (Single-variable Isolation Principle): Khi đo lường sự tiến bộ của phần mềm, nếu thay đổi đồng thời cả mã nguồn và bài thi, kết quả đo lường trở nên vô nghĩa. Đóng băng tập dữ liệu kiểm thử (Pinned Benchmark Set) là kỷ luật sắt của MLOps và SRE để bảo đảm mọi sự tăng giảm điểm số đều có thể quy kết trách nhiệm chính xác cho sự thay đổi mã lệnh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+DVC (Data Version Control) Documentation &amp; Hamel Husain: Evaluation Discipline for LLM Systems</t>
         </is>
       </c>
     </row>
@@ -956,10 +1016,26 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nguyên nhân vẫn là hypothesis cho tới khi test.
-Phân tích theo nguyên lý thiết kế: Nguyên nhân vẫn là hypothesis cho tới khi test.</t>
+- 1.0đ: Thiết lập giả thuyết nguyên nhân gốc rõ ràng, tập trung vào sự cố mất/sai cache key tải dependency.
+- 1.0đ: Phân biệt được hai giả thuyết cạnh tranh (nghẽn mạng do thiếu cache vs chậm do biên dịch/I/O).
+- 1.0đ: Thiết kế bài kiểm tra đối chứng (pre-warmed cache test) có thể thực thi ngay lập tức.
+- 1.0đ: Đưa ra tiêu chí kết luận định lượng rõ ràng xác nhận hoặc bác bỏ giả thuyết dựa trên kết quả test.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết lập Giả thuyết Nguyên nhân Gốc (Root-Cause Hypothesis) và Bài Kiểm tra Phân biệt (Distinguishing Test):
+1. **Giả thuyết Nguyên nhân Gốc (Falsifiable Root-Cause Hypothesis)**:
+- *Quan sát ban đầu*: Thời gian build bị chậm kéo dài tới 18 phút; biểu đồ trace phân tán chỉ ra rằng khâu tải gói phụ thuộc (dependency download) lặp đi lặp lại ở mọi job độc lập; cơ chế cache phụ thuộc chưa được kiểm chứng.
+- *Giả thuyết khoa học*: **Thời gian build bị kéo dài 18 phút là do bộ đệm lưu trữ gói phụ thuộc (CI Runner Dependency Cache, ví dụ npm/pip cache) bị vô hiệu hóa hoặc cấu hình sai khóa băm cache key**, dẫn đến việc mỗi container worker khi khởi động đều phải tải lại từ đầu toàn bộ các thư viện qua mạng Internet công cộng với tốc độ nghẽn băng thông, thay vì đọc tức thì từ local cache trong vài giây.
+2. **Thiết kế Bài Kiểm tra Phân biệt để Xác nhận hoặc Bác bỏ (Distinguishing Test)**:
+- **Mục tiêu**: Phân biệt dứt khoát giữa hai giả thuyết cạnh tranh: Lỗi do Tải mạng thiếu cache (Hypothesis A) vs Lỗi do Quá trình biên dịch/chạy test bên trong chậm (Hypothesis B).
+- **Giao thức Thực hiện Thực nghiệm có Đối chứng**:
+  + Tạo một nhánh thử nghiệm (test branch), cấu hình một job CI duy nhất với bộ cache được nạp sẵn thủ công (Pre-warmed local cache injection) hoặc gắn volume lưu sẵn thư mục `node_modules` / `.venv` trên runner.
+  + Chạy lệnh build và quan sát thời gian của từng span trong trace:
+    * **Nếu thời gian của bước dependency giảm từ 18 phút xuống dưới 30 giây VÀ tổng thời gian build giảm tương ứng**: **XÁC NHẬN 100% GIẢ THUYẾT A** (Nguyên nhân do mất cache mạng).
+    * **Nếu dependency vẫn mất nhiều thời gian dù đã có cache**: BÁC BỎ Giả thuyết A; chuyển mũi điều tra sang phân tích xung đột ổ đĩa I/O hoặc script post-install độc hại.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Giả thuyết Khoa học trong Chẩn đoán Hạ tầng (Hypothesis-Driven Troubleshooting): Một phỏng đoán chỉ trở thành giả thuyết kỹ thuật khi nó có thể bị bác bỏ (falsifiable) và đi kèm một bài kiểm tra phân biệt rõ ràng. Thay vì lao vào sửa mò cấu hình CI, việc thiết lập giả thuyết về cache key và thực hiện một bài test có nạp sẵn cache giúp cô lập chính xác nguyên nhân gốc chỉ trong một lần chạy thử.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Diagnosing System Problems &amp; Martin Fowler: Continuous Delivery - Deployment Pipeline</t>
         </is>
       </c>
     </row>
@@ -1038,10 +1114,26 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Follow-up phải phân biệt hai cause cạnh tranh.
-Phân tích theo nguyên lý thiết kế: Follow-up phải phân biệt hai cause cạnh tranh.</t>
+- 1.0đ: Phân tích đúng bản chất gây nhiễu khi đổi đồng thời cả Embedding và Chunking trong một release.
+- 1.0đ: Thiết kế thí nghiệm nhỏ nhất (giữ nguyên chunking cũ, chỉ test embedding mới trên tập truy vấn mẫu).
+- 1.0đ: Giải thích lý do vì sao phương án này là tối ưu về tài nguyên (không cần re-chunk lại toàn bộ kho dữ liệu).
+- 1.0đ: Thiết lập cây quyết định phân bổ nguyên nhân rạch ròi dựa trên kết quả của bài test đơn biến.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Thử nghiệm Kế tiếp Nhỏ nhất để Tạo Bằng chứng Phân bổ Nguyên nhân (Smallest Follow-up Experiment for Attribution):
+1. **Bản chất Thách thức Nhiễu Lẫn (Confounded Dual-Change Problem)**:
+Tỷ lệ truy xuất thất bại (retrieval miss rate) tăng đột biến sau đợt release, nhưng trong đợt release này đội ngũ đã **thay đổi đồng thời cả hai yếu tố**: nâng cấp phiên bản mô hình embedding (Embedding Version) VÀ thay đổi chiến lược phân mảnh văn bản (Chunking Strategy). Hai biến số này triệt tiêu hoặc khuếch đại lẫn nhau, khiến việc đổ lỗi cho embedding hay chunking là hoàn toàn thiếu căn cứ.
+2. **Thiết kế Thử nghiệm Nhỏ nhất Cô lập Biến số (Minimal 1-Variable Ablation Experiment)**:
+- **Nguyên tắc**: Giữ cố định 1 biến số ở trạng thái cũ và chỉ đổi 1 biến số duy nhất trên cùng một tập 100 câu hỏi truy vấn mẫu có sẵn:
+- **Giao thức Thực hiện 1 Bước Tối thiểu**:
+  + **Cố định Chunking Cũ**, chỉ chạy so sánh: `Embedding Cũ` vs `Embedding Mới` trên tập dữ liệu đã phân mảnh cũ.
+  + (Phương án này là nhỏ nhất vì không cần phải index lại toàn bộ văn bản theo chunking mới, tiết kiệm 90% thời gian và chi phí tính toán).
+3. **Cơ chế Phân bổ Trách nhiệm (Attribution Decision Logic)**:
+- **Trường hợp 1**: Nếu trên cùng chunking cũ, `Embedding Mới` làm retrieval miss tăng tương tự như trên production -&gt; **Khẳng định 100% nguyên nhân do Embedding Version** (mô hình mới không tương thích với miền thuật ngữ của tài liệu).
+- **Trường hợp 2**: Nếu trên chunking cũ, `Embedding Mới` có điểm số tốt hoặc tương đương bản cũ -&gt; **Khẳng định nguyên nhân do Chunking Strategy Mới** (chiến lược cắt đoạn mới làm vỡ ngữ cảnh thông tin hoặc kích thước chunk quá nhỏ/quá lớn).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thử nghiệm Triệt tiêu Tối thiểu (Minimal Ablation Study in MLOps): Khi hai thành phần cốt lõi của RAG cùng đổi một lúc, cách nhanh nhất và rẻ nhất để tìm ra thủ phạm không phải là phân tích lý thuyết, mà là thực hiện một thí nghiệm bóc tách đơn biến (Single-variable ablation). Giữ nguyên dữ liệu chunking cũ và chỉ đổi mô hình embedding là phép thử tốn ít tài nguyên nhất để đưa ra kết luận phân bổ nguyên nhân với độ tin cậy tuyệt đối.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Chip Huyen: Designing Machine Learning Systems (Ablation Studies) &amp; Pinecone: Chunking Strategies for LLM Applications</t>
         </is>
       </c>
     </row>
@@ -1072,10 +1164,27 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một pattern cần link về ví dụ đóng góp và điều kiện không áp dụng.
-Phân tích theo nguyên lý thiết kế: Một pattern cần link về ví dụ đóng góp và điều kiện không áp dụng.</t>
+- 1.0đ: Ánh xạ chuẩn xác nguồn gốc dữ liệu (Provenance) của cả 4 ghi chú (A, B, C, D).
+- 1.0đ: Tổng hợp được khuôn mẫu chủ đạo (Uncoordinated Schema Drift) từ Note A và B có trace chứng minh.
+- 1.0đ: Tích hợp góc nhìn tổ chức về thiếu ownership từ Note C vào bức tranh căn nguyên sâu xa.
+- 1.0đ: Bảo toàn trọn vẹn bằng chứng thiểu số của Note D, phân tách rõ lỗi nội bộ vs lỗi vendor bên ngoài.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Tổng hợp Khuôn mẫu Nhóm (Group Pattern Synthesis) Bảo toàn Nguồn gốc (Provenance) và Bằng chứng Thiểu số (Minority Evidence):
+1. **Bản đồ Nguồn gốc Bằng chứng Độc lập (Evidence Provenance Map)**:
+- Note A: Nêu hiện tượng Schema Drift giữa Service 1 và Service 2 (có trace link `tr-001`).
+- Note B: Nêu hiện tượng Schema Drift tại Event Bus Gateway (có trace link `tr-002`).
+- Note C: Phản ánh góc nhìn tổ chức: thiếu sự phân định trách nhiệm rõ ràng (lack of schema ownership) giữa các team.
+- Note D: **Bằng chứng Thiểu số Đối kháng (Minority Counter-evidence)**: Phản đối rằng có ít nhất một ca drift không phải do nội bộ, mà do nhà cung cấp bên thứ ba (Source Vendor) tự ý thay đổi API payload mà không thông báo trước.
+2. **Tổng hợp Khuôn mẫu Hợp nhất có Phân nhánh (Synthesized Multi-causal Pattern)**:
+- **Khuôn mẫu Cốt lõi (Dominant Pattern)**: **Đứt gãy Tương thích Dữ liệu do Thay đổi Lược đồ Không Kiểm soát (Uncoordinated Schema Drift)**. Hiện tượng này được củng cố bởi bằng chứng kỹ thuật có trace thực tế từ Note A và B.
+- **Bảo toàn Căn nguyên Tổ chức (Organizational Provenance)**: Note C giải thích *tại sao* điều này xảy ra trong nội bộ: do thiếu quy trình Schema Registry và thiếu người sở hữu hợp đồng dữ liệu (Data Contract Owner).
+- **Bảo toàn Bằng chứng Thiểu số (Preserving Minority Evidence from Note D)**: Tuyệt đối không được gạt bỏ Note D như một ngoại lệ không quan trọng! Bản báo cáo hậu kiểm phải phân tách rõ ràng thành hai nhánh nguyên nhân độc lập:
+  + **Nhánh 1 (Nội bộ - 75%)**: Schema drift giữa các vi dịch vụ nội bộ do thiếu ownership (Khắc phục: Áp dụng Protobuf / JSON Schema validation trong CI).
+  + **Nhánh 2 (Ngoại cảnh - 25%)**: Schema drift do Vendor bên ngoài đổi cấu trúc (Khắc phục: Bổ sung Ingestion Adapter phòng thủ và hợp đồng SLA với Vendor).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Tôn trọng Tiếng nói Thiểu số trong Phân tích Hậu kiểm (Minority Evidence &amp; Provenance Preservation): Sai lầm phổ biến của các cuộc họp postmortem là 'tư duy đồng thuận bầy đàn' (Groupthink) - gạt bỏ các ý kiến phản đối để chọn một nguyên nhân đơn giản nhất. Bằng chứng thiểu số của Note D chỉ ra một rủi ro hoàn toàn khác (Vendor Drift). Một bản tổng hợp chuyên nghiệp phải giữ nguyên nguồn gốc từng bằng chứng và tích hợp các góc nhìn thiểu số vào danh sách hành động phòng ngừa.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Being Benign and Blameless &amp; Sidney Dekker: The Field Guide to Understanding 'Human Error'</t>
         </is>
       </c>
     </row>
@@ -1106,10 +1215,26 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Frequency không xóa cause khác hoặc case thiếu evidence.
-Phân tích theo nguyên lý thiết kế: Frequency không xóa cause khác hoặc case thiếu evidence.</t>
+- 1.0đ: Phân loại định lượng chính xác 3 nhóm từ 6 ca: 4 ca vendor, 1 ca deadlock, 1 ca không có trace.
+- 1.0đ: Tổng hợp đúng khuôn mẫu chủ đạo (External Vendor Dependency) chiếm 66.7%.
+- 1.0đ: Bảo toàn trọn vẹn ca ngoại lệ Deadlock, lý giải vì sao không được phép coi đây là lỗi vendor.
+- 1.0đ: Xử lý đúng đắn ca thiếu trace thành bài học về lỗ hổng quan sát (telemetry gap) cần khắc phục.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Tổng hợp Khuôn mẫu (Group Pattern Synthesis) và Bảo toàn Ngoại lệ &amp; Dữ liệu Khuyết thiếu (Preserving Exceptions &amp; Unknowns):
+1. **Bảng Phân tích Hiện trạng 6 Ghi chú Sự cố (Fact Synthesis Matrix)**:
+- Tổng số ca quan sát: $N = 6$ ca sự cố timeout.
+- Nhóm 1 (Đa số - 4 ca): Timeout phát sinh do độ trễ dịch vụ của nhà cung cấp bên ngoài (API Vendor Timeout).
+- Nhóm 2 (Ngoại lệ - 1 ca): Timeout phát sinh do bế tắc tranh chấp tài nguyên nội bộ (Internal Concurrency Deadlock).
+- Nhóm 3 (Dữ liệu Khuyết thiếu - 1 ca): Ca timeout **hoàn toàn không có dữ liệu trace (No Trace Available)**.
+2. **Tổng hợp Khuôn mẫu Chuẩn mực (Synthesized Pattern)**:
+- **Khuôn mẫu Thống trị (Dominant Failure Pattern: 66.7%)**: **Sự phụ thuộc thiếu kiên cường vào Hạ tầng Đối tác Bên ngoài (External Vendor Dependency Vulnerability)**. 4 trên 6 ca sự cố là do API bên thứ ba bị quá tải làm nghẽn luồng xử lý của ứng dụng.
+3. **Bảo tồn Ngoại lệ và Dữ liệu Khuyết thiếu (Preserving Exceptions and Unknowns)**:
+- **Bảo tồn Ngoại lệ Deadlock (Preserving the Deadlock Exception - 16.7%)**: Tuyệt đối không được xóa bỏ ca Deadlock để kết luận đơn giản 'mọi lỗi là do Vendor'. Ca Deadlock chứng minh hệ thống nội bộ đang tiềm ẩn một lỗi kiến trúc đa luồng nghiêm trọng độc lập với vendor. Hành động: Tạo riêng một vé Jira P1 điều tra cơ chế khóa (locking mechanism) của database.
+- **Bảo tồn và Phản ánh Dữ liệu Khuyết thiếu (Preserving Unknowns / Zero-Trace - 16.7%)**: Ca không có trace phải được phân loại rõ ràng là **'TRẠNG THÁI KHÔNG THỂ XÁC ĐỊNH DO ĐỨT GÃY QUAN SÁT (UNKNOWN DUE TO TELEMETRY GAP)'**. Hành động: Đây là bằng chứng chỉ ra một lỗ hổng quan sát (Observability Blind Spot) - cần bổ sung instrumentation ngay lập tức cho endpoint này.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản trị Sự thật trong Phân tích Hệ thống (Preserving Exceptions and Unknowns in Failure Synthesis): Quy luật số đông (Frequency) không bao giờ có quyền xóa bỏ các nguyên nhân khác hoặc xóa bỏ các ca thiếu bằng chứng. Nếu chỉ nhìn vào 4 ca do Vendor, nhóm kỹ sư sẽ bỏ qua quả bom nổ chậm Deadlock trong nội bộ; và nếu bỏ qua ca không có trace, lỗ hổng mù giám sát sẽ tiếp tục tồn tại. Một bản tổng hợp trung thực phải phân loại đầy đủ: Đa số, Ngoại lệ, và Không xác định.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+John Allspaw: Trade-Offs in Resilience Engineering &amp; Google SRE Workbook: Incident Tracking</t>
         </is>
       </c>
     </row>
@@ -1192,10 +1317,39 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ledger không phải checklist vendor.
-Phân tích theo nguyên lý thiết kế: Ledger không phải checklist vendor.</t>
+- 1.0đ: Thiết kế lược đồ Fact Ledger đầy đủ các trường thiết yếu (id, source, hard/soft type, statement, conflict status).
+- 1.0đ: Phân tích đúng bản chất mâu thuẫn về cloud logging giữa yêu cầu bảo mật và nhu cầu vận hành.
+- 1.0đ: Đưa ra giải pháp kỹ thuật hòa giải sáng tạo thỏa mãn cả hai bên (Hybrid Gateway: raw on-prem, redacted/metric to cloud).
+- 1.0đ: Khẳng định nguyên tắc quy trình: chỉ được chọn topology sau khi toàn bộ xung đột trong sổ cái đã được giải quyết.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Lược đồ Sổ cái Sự thật Kịch bản (Enterprise Scenario Fact Ledger Schema) và Quy trình Xử lý Xung đột:
+1. **Thiết kế Lược đồ Sổ cái Sự thật (Fact Ledger Schema)**:
+```json
+{
+  "fact_id": "FACT-BANK-009",
+  "stakeholder_source": "Security | Operations | Product | Legal | Compliance",
+  "domain": "data_protection | network | latency | logging | cost",
+  "constraint_type": "HARD_MANDATORY | SOFT_PREFERENCE | UNKNOWN_ASSUMPTION",
+  "statement_text": "Toàn bộ log giao dịch ngân hàng bắt buộc phải lưu trữ on-premise, cấm đẩy ra cloud.",
+  "regulatory_driver": "Nghị định 13/2023/NĐ-CP &amp; Tiêu chuẩn Ngân hàng Nhà nước về an toàn dữ liệu",
+  "status": "CONFIRMED | CONFLICTED | SUPERSEDED",
+  "conflicting_fact_ids": ["FACT-BANK-010"],
+  "resolution_status": "UNRESOLVED | RESOLVED_BY_ARCH_BOARD"
+}
+```
+2. **Quy trình Xử lý Mâu thuẫn về Cloud Logging Trước khi Chọn Topology (Conflict Resolution Workflow)**:
+- **Bối cảnh mâu thuẫn**: Bên Security tuyên bố 'Cấm đẩy log ra Cloud', nhưng bên Ops tuyên bố 'Cần đẩy toàn bộ log lên Cloud SaaS Datadog để on-call trực chiến 24/7'.
+- **Bước 1: Bóc tách Căn cứ Pháp lý vs Nhu cầu Vận hành**:
+  Truy vấn nguồn gốc của Security: 'Cấm đẩy log' thực chất là cấm đẩy **Dữ liệu Cá nhân Khách hàng (PII) và Số tài khoản (Raw Transaction Data)** ra hạ tầng công cộng.   Trong khi đó, nhu cầu của Ops chỉ là cần nhìn thấy **Chỉ số Kỹ thuật (Error Rate, Latency, Stack Trace đã khử khuẩn)** để gỡ lỗi.
+- **Bước 2: Hội đồng Kiến trúc Hòa giải Kỹ thuật (Architectural Resolution)**:
+  Đưa ra giải pháp thỏa mãn 100% cả hai bên: **Mô hình Hybrid Telemetry Gateway**:
+  + Toàn bộ Raw Logs chứa dữ liệu ngân hàng được lưu giữ 100% tại máy chủ On-premise (thỏa mãn Security).
+  + Một Agent tại On-premise tiến hành khử khuẩn PII (redaction) và chỉ đẩy các Metric tổng hợp không danh tính sang Cloud Dashboard (thỏa mãn Ops).
+- **Bước 3: Khóa Sổ cái (Freeze Ledger)**: Cập nhật trạng thái `FACT-BANK-009` và `010` thành `RESOLVED`. Chỉ khi sổ cái không còn xung đột, nhóm kiến trúc mới được phép chọn Topology.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Sổ cái Sự thật trong Kiến trúc Doanh nghiệp (Enterprise Fact Ledger &amp; Conflict Resolution): Trong các tổ chức tài chính lớn, việc vội vàng chọn Topology (Cloud vs On-prem) khi các phòng ban vẫn đang mâu thuẫn là nguyên nhân hàng đầu khiến dự án thất bại. Sổ cái Sự thật biến các phát biểu cảm tính thành các bản ghi có căn cứ pháp lý và phân loại cứng/mềm. Giải quyết xung đột ở tầng dữ liệu trước khi chọn topology bảo đảm kiến trúc được chọn luôn vững vàng trước mọi cuộc thanh tra.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+TOGAF Enterprise Architecture Framework: Stakeholder Management &amp; Banking Cloud Compliance Standards (PCI-DSS, Basel III)</t>
         </is>
       </c>
     </row>
@@ -1280,10 +1434,22 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân loại phải kèm hậu quả quyết định.
-Phân tích theo nguyên lý thiết kế: Phân loại phải kèm hậu quả quyết định.</t>
+- 1.0đ: Phân loại đúng Legal statement là Unknown/Unverified và đưa ra action yêu cầu văn bản pháp lý chính thức.
+- 1.0đ: Phân loại đúng SRE RTO &lt;= 15m là Hard Constraint và đưa ra action thiết kế automated failover.
+- 1.0đ: Phân loại đúng CFO thích OPEX là Soft Constraint và giải thích mối quan hệ thứ bậc trước ràng buộc cứng.
+- 1.0đ: Phân loại đúng Peak load chưa đo là Unknown và đưa ra action thực hiện load testing khẩn cấp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân loại Bốn Phát biểu Doanh nghiệp thành Ràng buộc Cứng, Ràng buộc Mềm, và Đại lượng Chưa biết (Hard / Soft / Unknown) kèm Hành động:
+| Phát biểu Doanh nghiệp | Phân loại Chuẩn mực | Hành động Kỹ thuật &amp; Quản trị Bắt buộc |
+| :--- | :--- | :--- | :--- |
+| **1. Legal nói 'có thể cần local residency'** | **UNKNOWN / UNVERIFIED RISK** (Đại lượng Chưa biết / Rủi ro Mơ hồ) | **Hành động**: Yêu cầu phòng Pháp chế (Legal/Compliance) ban hành một **Văn bản Kết luận Pháp lý Chính thức (Formal Legal Memo)** dẫn chiếu rõ điều khoản luật. Tạm thời coi đây là rủi ro cao nhưng không vội mua sắm phần cứng on-premise đắt đỏ khi chưa có văn bản chính thức. |
+| **2. SRE yêu cầu RTO $\le$ 15 phút** | **HARD CONSTRAINT** (Ràng buộc Kỹ thuật Cứng Bắt buộc) | **Hành động**: Bắt buộc thiết kế kiến trúc có cơ chế **Chuyển đổi Dự phòng Tự động (Automated Failover)**, cụm Active-Passive hoặc Multi-region Hot Standby. Mọi phương án triển khai phục hồi thủ công mất &gt; 15 phút đều bị LOẠI BỎ NGAY LẬP TỨC. |
+| **3. CFO thích OPEX** | **SOFT CONSTRAINT / PREFERENCE** (Ràng buộc Mềm / Sở thích Tài chính) | **Hành động**: Ưu tiên lựa chọn các mô hình dịch vụ thanh toán theo dung lượng sử dụng (Cloud SaaS, API Pay-as-you-go) để tối ưu dòng tiền. Tuy nhiên, sở thích này **BỊ PHỦ QUYẾT** nếu nó mâu thuẫn với các Ràng buộc Cứng (như nếu luật bắt buộc on-premise). |
+| **4. Peak load chưa đo** | **UNKNOWN / CRITICAL GAP** (Đại lượng Chưa biết Chí mạng) | **Hành động**: Thực hiện ngay bài kiểm thử tải mô phỏng (Load &amp; Stress Testing) hoặc phân tích dữ liệu lịch sử của hệ thống lõi để đo lường thông lượng đỉnh (Peak TPS, Concurrency). Tuyệt đối không được ký hợp đồng hạ tầng khi chưa có con số peak load. |
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân định Ràng buộc trong Thiết kế Hệ thống Doanh nghiệp (Hard vs Soft vs Unknown Classification): Một kiến trúc sư trưởng phải phân biệt rạch ròi ba khái niệm: Ràng buộc Cứng (Hard) là luật lệ và cam kết sống còn không thể thương lượng (SRE RTO &lt;= 15m); Ràng buộc Mềm (Soft) là mong muốn có thể thỏa hiệp khi cần thiết (CFO thích OPEX); và Đại lượng Chưa biết (Unknown) là lỗ hổng thông tin nguy hiểm cần phải được xác minh bằng văn bản hoặc đo lường thực tế trước khi đưa ra quyết định hạ tầng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+SEI (Software Engineering Institute) Architecture Tradeoff Analysis Method (ATAM) &amp; TOGAF Standard</t>
         </is>
       </c>
     </row>
@@ -1362,10 +1528,29 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Trace từng payload qua boundary và hỏi ai được đọc/duyệt.
-Phân tích theo nguyên lý thiết kế: Trace từng payload qua boundary và hỏi ai được đọc/duyệt.</t>
+- 1.0đ: Thiết kế ranh giới phân vùng an toàn tuyệt đối (Raw PII giữ 100% on-prem, cloud chỉ nhận de-identified features).
+- 1.0đ: Đặc tả quy trình khử khuẩn và băm bảo mật tại On-prem Gateway trước khi truyền qua đám mây.
+- 1.0đ: Thiết lập cơ chế kiểm soát bắt buộc: quyết định từ chối vay (denial) phải có phê duyệt của con người (Human Approval Gate).
+- 1.0đ: Thiết kế nhật ký kiểm toán bất biến (Audit Trail) lưu giữ toàn bộ quyết định phục vụ thanh tra ngân hàng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hợp đồng Kiểm soát Dữ liệu (Enterprise Data-Control Contract) cho Luồng Tài chính Ngân hàng:
+1. **Bản đồ Vùng Dữ liệu và Ranh giới Rạch ròi (Data Boundary Topology)**:
+- **Vùng 1: On-premise Secure Banking Enclave (Nội bộ Ngân hàng)**:
+  + Lưu trữ toàn bộ dữ liệu giao dịch thô (`raw_transaction_data`) chứa thông tin PII nhạy cảm (Tên, CCCD, Số tài khoản, Số dư).
+  + Vận hành Module Khử khuẩn và Trích xuất Đặc trưng (De-identification &amp; Feature Extraction Gateway).
+- **Vùng 2: Cloud AI Inference Zone (Môi trường Đám mây)**:
+  + Tuyệt đối **KHÔNG BAO GIỜ** nhận dữ liệu thô. Chỉ tiếp nhận các vector đặc trưng số học đã được phi danh tính hóa (Tokenized Features: ví dụ `feature_credit_ratio: 0.42`, `feature_stability_index: 8.5`).
+2. **Hợp đồng Luồng Dữ liệu Xuyên Ranh giới (Cross-boundary Flow Contract)**:
+- **Bước 1: Ingestion &amp; De-identification (Tại On-prem)**: Hệ thống on-prem băm một chiều danh tính thành `pseudo_client_id = HMAC(client_id, secret_salt)` và chỉ gửi các trường phi PII lên Cloud qua kênh mã hóa mTLS.
+- **Bước 2: Cloud Inference (Tại Cloud)**: Mô hình AI tính toán xác suất rủi ro tín dụng và trả về dự đoán (`risk_score: 0.82`, `recommendation: REJECT`).
+- **Bước 3: Rào chắn Phê duyệt Con người cho Quyết định Từ chối (Human-in-the-Loop for Rejections)**:
+  + Theo quy định tín dụng: **Mọi quyết định Từ chối vay (Loan Denial) đều không được phép tự động hóa hoàn toàn**.
+  + Khi AI đề xuất `REJECT`, quyết định này được chuyển vào hàng đợi `Pending_Human_Review` tại On-premise.   Cán bộ tín dụng con người (Credit Officer) phải mở hồ sơ, xem xét lý do giải trình của AI, và ký số phê duyệt (Sign-off) thì quyết định từ chối mới có hiệu lực pháp lý.
+- **Bước 4: Nhật ký Kiểm toán Bất biến (Immutable Audit Logging)**: Toàn bộ chuỗi sự kiện (Input features, AI recommendation, Credit officer ID, Timestamp, Justification) được ghi vào kho lưu trữ WORM on-premise để phục vụ thanh tra tài chính.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Kiểm soát Dữ liệu Ngân hàng Xuyên Biên giới (Financial Data Control Contract &amp; Ethical AI): Tuân thủ các đạo luật bảo vệ người tiêu dùng tài chính (như Equal Credit Opportunity Act - ECOA và GDPR Article 22), các quyết định có tác động pháp lý tiêu cực đến quyền lợi của khách hàng (như từ chối cho vay) bắt buộc phải có sự tham gia của con người (Human-in-the-loop). Kết hợp với cổng khử khuẩn dữ liệu ở ranh giới On-premise bảo đảm thông tin tài chính cá nhân không bao giờ bị rò rỉ ra hạ tầng đám mây công cộng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Basel Committee on Banking Supervision: Sound Practices for Operational Resilience &amp; GDPR Article 22 (Automated Individual Decision-making)</t>
         </is>
       </c>
     </row>
@@ -1396,10 +1581,29 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không tự coi embedding là non-sensitive.
-Phân tích theo nguyên lý thiết kế: Không tự coi embedding là non-sensitive.</t>
+- 1.0đ: Thiết lập ranh giới kiểm soát rõ ràng cho Raw Note (on-prem), Model Output (redacted), và Audit Log (HIPAA WORM).
+- 1.0đ: Khẳng định nguyên tắc an toàn: tuyệt đối không tự ý coi vector embedding là dữ liệu an toàn/phi nhạy cảm.
+- 1.0đ: Phân tích cơ sở khoa học về rủi ro bảo mật của embedding (Embedding Inversion Attacks tái tạo lại văn bản gốc).
+- 1.0đ: Đưa ra hành động xử lý Unknown mẫu mực (khóa embedding on-prem, triển khai vector DB nội bộ, xin phê duyệt pháp chế).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Kiểm soát Ranh giới Y tế (Healthcare Data Control) và Xử lý Đại lượng Chưa biết (Handling Unknowns for Embeddings):
+1. **Bản đồ Ranh giới Kiểm soát Dữ liệu Y tế (Healthcare Boundary Controls)**:
+- **Tài sản 1: Bệnh án thô (Raw Clinical Notes)**: Chứa thông tin bệnh sử, tên tuổi, chẩn đoán (Protected Health Information - PHI). Theo chính sách: **CẤM TUYỆT ĐỐI KHÔNG ĐƯỢC RỜI ON-PREMISE SITE**.
+- **Tài sản 2: Đầu ra mô hình (Model Output)**: Báo cáo tóm tắt hoặc gợi ý lâm sàng. Chỉ được phép xuất viện sau khi đã qua bộ lọc khử khuẩn PHI tự động và được bác sĩ ký duyệt.
+- **Tài sản 3: Nhật ký Kiểm toán (Audit Log)**: Lưu trữ nội bộ on-premise trên hạ tầng WORM phục vụ tuân thủ đạo luật HIPAA trong tối thiểu 6 năm.
+2. **Xử lý Đại lượng Chưa biết đối với Vector Embedding (Handling the Unknown Policy on Embeddings)**:
+- **Hiện trạng Chính sách**: Chính sách cấm bệnh án thô ra ngoài nhưng **CHƯA ĐỀ CẬP** việc liệu Vector Embedding có được phép rời site hay không.
+- **Nguyên tắc Phòng ngừa Tối đa (The Precautionary Principle in AI Healthcare)**:
+  + **TUYỆT ĐỐI KHÔNG TỰ COI VECTOR EMBEDDING LÀ DỮ LIỆU VÔ HẠI (NON-SENSITIVE)**!
+  + *Lý do kỹ thuật*: Các nghiên cứu bảo mật gần đây (như Embedding Inversion Attacks / Vec2Text) đã chứng minh rằng các vector embedding có thể bị dịch ngược (reconstructed) để tái tạo lại gần như nguyên vẹn tới 70-90% văn bản gốc, bao gồm cả các tên thuốc và triệu chứng bệnh án nhạy cảm.
+- **Hành động Vận hành &amp; Kiểm soát Kiến trúc Bắt buộc**:
+  + **Hành động 1 (Khóa Ranh giới Tức thì)**: Mặc định coi Embedding có cấp độ nhạy cảm ngang hàng với Bệnh án thô: **CẤM Vector Embedding rời khỏi site On-premise** cho đến khi có quy định chính thức.
+  + **Hành động 2 (Kiến trúc On-prem Vector DB)**: Triển khai Vector Database (Milvus/Qdrant) ngay trên máy chủ On-premise để phục vụ truy vấn nội bộ.
+  + **Hành động 3 (Trình Hội đồng Pháp lý)**: Gửi văn bản đề xuất lên Hội đồng Bảo mật Y tế và Pháp chế để xin ý kiến hướng dẫn chính thức bằng văn bản.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản trị An toàn Vector Embedding trong Y tế (Vector Privacy &amp; Embedding Inversion Risk): Một quan niệm sai lầm rất nguy hiểm là coi embedding chỉ là 'các dãy số thực vô hại'. Với các kỹ thuật tấn công đảo ngược vector hiện đại, việc đẩy embedding lên cloud SaaS đồng nghĩa với việc đẩy gián tiếp bệnh án của bệnh nhân lên mạng. Áp dụng nguyên tắc phòng ngừa (Precautionary Principle) - coi mọi dữ liệu chưa rõ chính sách là Dữ liệu Tuyệt mật - là nghĩa vụ đạo đức và pháp lý của kỹ sư y tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Morris et al.: Text Embeddings Reveal (Almost) As Much As Text (EMNLP 2023) &amp; HIPAA Privacy and Security Rules for PHI</t>
         </is>
       </c>
     </row>
@@ -1430,10 +1634,33 @@
       <c r="K23" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi fact phải nối tới một test feasibility hoặc operating risk.
-Phân tích theo nguyên lý thiết kế: Mỗi fact phải nối tới một test feasibility hoặc operating risk.</t>
+- 1.0đ: Chuyển đổi sự thật MES batch file thành ràng buộc adapter và kịch bản test file ingestion.
+- 1.0đ: Chuyển đổi sự thật mất mạng WAN 20 phút thành ràng buộc offline autonomy $\ge 30$ phút kèm test đệm dữ liệu.
+- 1.0đ: Chuyển đổi giới hạn GPU 16GB và peak 40 req/s thành giới hạn VRAM (&lt;12GB) và bài kiểm thử tải thông lượng.
+- 1.0đ: Nhận diện chính xác ngưỡng còn thiếu chí mạng: Tỷ lệ báo động sai (False Alarm Rate / FPR) khi kích hoạt dừng dây chuyền.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Chuyển đổi các Sự thật Thành Ràng buộc Vận hành Kiểm thử được (Testable Operating Constraints) và Xác định Ngưỡng còn Thiếu:
+1. **Bảng Chuyển đổi Sự thật Thành Ràng buộc Kiểm thử được (Fact-to-Constraint Mapping)**:
+- **Sự thật 1: MES Legacy chỉ hỗ trợ batch file**:
+  + *Operating Constraint*: Hệ thống Edge AI không được đòi hỏi REST API/gRPC từ MES; bắt buộc phải có module File Ingestion Adapter hỗ trợ đọc và ghi các file định dạng phẳng (CSV/XML) theo chu kỳ định sẵn.
+  + *Acceptance Test*: Bơm file CSV 10.000 dòng vào thư mục chia sẻ SMB; xác nhận adapter đọc trọn vẹn và không làm hỏng file gốc.
+- **Sự thật 2: Mạng WAN mất tối đa 20 phút/ngày**:
+  + *Operating Constraint*: Hệ thống tại biên (Edge) phải có khả năng **Tự chủ Hoạt động Ngoại tuyến (Autonomous Offline Operation) tối thiểu 30 phút** (có vùng đệm an toàn 1.5x so với 20 phút WAN đứt).
+  + *Acceptance Test*: Ngắt kết nối cáp mạng WAN trong 25 phút; dây chuyền vẫn hoạt động 100%, dữ liệu được đệm an toàn tại SQLite/Queue cục bộ và tự động đồng bộ lại khi có mạng.
+- **Sự thật 3: Edge GPU 16 GB bộ nhớ**:
+  + *Operating Constraint*: Toàn bộ mô hình AI, runtime context và bộ đệm bộ nhớ (VRAM consumption) **không được vượt quá 12 GB** (dành 4 GB dự phòng cho CUDA context và OS).
+  + *Acceptance Test*: Đo lường `nvidia-smi` dưới tải nặng liên tục trong 4 giờ; xác nhận không xảy ra lỗi CUDA Out-Of-Memory (OOM).
+- **Sự thật 4: Tải đỉnh Peak 40 req/s**:
+  + *Operating Constraint*: Edge runtime phải xử lý thông lượng bền vững $\ge 40$ requests/giây với độ trễ P99 $\le 200$ ms.
+  + *Acceptance Test*: Chạy load test giả lập 50 req/s bằng Locust; xác nhận tỷ lệ rớt gói bằng 0%.
+2. **Ngưỡng Kỹ thuật Còn Thiếu Bắt buộc Phải Làm rõ (Missing Critical Threshold)**:
+- **Ngưỡng Báo động Sai (False Alarm Rate / False Positive Rate - FPR) của Cảnh báo Dừng Dây chuyền**:
+  + Đề bài nêu: 'Cảnh báo sai có thể dừng dây chuyền' (mỗi lần dừng dây chuyền nhà máy thiệt hại hàng tỷ đồng), nhưng **chưa hề cho biết ngưỡng FPR chấp nhận được là bao nhiêu**!
+  + *Ngưỡng cần bổ sung*: Yêu cầu xác lập chỉ số định lượng: Tỷ lệ báo động sai $\text{FPR} \le 0.001\%$ (tối đa 1 báo động sai trên 100.000 sản phẩm),   đồng thời bổ sung cơ chế xác nhận kép (Two-stage visual verification) trước khi gửi tín hiệu ngắt khẩn cấp PLC của nhà máy.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đặc tả Ràng buộc Kỹ nghệ Hệ thống Biên (Edge System Operating Constraints): Một sự thật vận hành (như mất mạng 20 phút, GPU 16GB) là vô dụng nếu không được chuyển thành một bài kiểm thử tự động có ngưỡng đo cụ thể (Testable Acceptance Rule). Đặc biệt, trong sản xuất công nghiệp, việc thiếu ngưỡng sai số cho các hành động có hậu quả cao (như dừng dây chuyền) là lỗi kiến trúc nguy hiểm nhất; kỹ sư phải chủ động chỉ ra khoảng trống này để xác lập tiêu chuẩn an toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+IEC 61508 / IEC 62443 Industrial Communication Networks and Systems Safety &amp; Edge AI Deployment Guidelines</t>
         </is>
       </c>
     </row>
